--- a/reports/一级子公司A_现金流量表_2026-11.xlsx
+++ b/reports/一级子公司A_现金流量表_2026-11.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>148066620</v>
+        <v>145513177</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1669159908</v>
+        <v>1645829693</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>2911659</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>33355612</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1451767</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>16656983</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>725616</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>8340098</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>582524</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>6662809</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>434166</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>5003322</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>291874</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>3332329</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>216814</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2500715</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>145970</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1666898</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>361647</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>4165960</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>183081</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2095195</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>115275</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1324101</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>379658</v>
+        <v>374455</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4356282</v>
+        <v>4299181</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2697570</v>
+        <v>2666660</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>30952530</v>
+        <v>30530157</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>151143848</v>
+        <v>155974685</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>95913600</v>
+        <v>94132288</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1100534400</v>
+        <v>1085048215</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>972201</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>11115921</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>724400</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>8329816</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>484794</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>5559703</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>363327</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>4164116</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>241627</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>2779987</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>183128</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2092940</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>15685870</v>
+        <v>15408780</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>179983230</v>
+        <v>177661254</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>7992800</v>
+        <v>7920964</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>91711200</v>
+        <v>90418470</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3297030</v>
+        <v>3237274</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>37830870</v>
+        <v>37331469</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>122889300</v>
+        <v>123668783</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>28254548</v>
+        <v>32305902</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>185400</v>
+        <v>182316</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2039400</v>
+        <v>2014194</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1545000</v>
+        <v>1516404</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>16995000</v>
+        <v>16767446</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>947600</v>
+        <v>939533</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>10423600</v>
+        <v>10285330</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1730400</v>
+        <v>1698720</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14420000</v>
+        <v>14224280</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>158620000</v>
+        <v>156053666</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2060000</v>
+        <v>2020532</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>22660000</v>
+        <v>22249990</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10300000</v>
+        <v>10136266</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>113300000</v>
+        <v>111565303</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>391400</v>
+        <v>384154</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>4305400</v>
+        <v>4247503</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14811400</v>
+        <v>14608434</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-13081000</v>
+        <v>-12909714</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3605000</v>
+        <v>3550419</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>39655000</v>
+        <v>39139248</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5665000</v>
+        <v>5592267</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>62315000</v>
+        <v>61444868</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5665000</v>
+        <v>5578963</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>62315000</v>
+        <v>61534545</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>185400</v>
+        <v>183611</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2039400</v>
+        <v>2011714</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9455400</v>
+        <v>9326297</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4635000</v>
+        <v>4597461</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>50985000</v>
+        <v>50310712</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4635000</v>
+        <v>4552331</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>50985000</v>
+        <v>50327575</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>741600</v>
+        <v>735281</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>8157600</v>
+        <v>8053504</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>648900</v>
+        <v>641928</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>7137900</v>
+        <v>7049598</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>92700</v>
+        <v>91438</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1019700</v>
+        <v>1005799</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5469300</v>
+        <v>5424180</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3986100</v>
+        <v>3902117</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>19159648</v>
+        <v>23298305</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>19159648</v>
+        <v>23298305</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
